--- a/Data Appendix/CH_Hazard_Checklist.xlsx
+++ b/Data Appendix/CH_Hazard_Checklist.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Honours\Data Appendix\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/48f02162ba686543/Other/Documents/GitHub/NVP_Honours_Data/Data Appendix/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{423337BB-9851-40A8-83B2-C8E81C15A5A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{423337BB-9851-40A8-83B2-C8E81C15A5A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{838A4ECB-39DC-4C22-9B2C-2BD0943ABA9A}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="4" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Index" sheetId="8" r:id="rId1"/>
@@ -148,9 +148,6 @@
     <t>If volcanic eruption has produced a lahar in recorded history, or geological evidence of lahar exists</t>
   </si>
   <si>
-    <t>If volcano has a source of permanent water/ice on edifice, water volume &gt;10^6 m3, or there is a known aquifer underground</t>
-  </si>
-  <si>
     <t>Slope &gt;25%</t>
   </si>
   <si>
@@ -298,9 +295,6 @@
   </si>
   <si>
     <t>Lava delta collapse is the primary cause of ocean entry hazards</t>
-  </si>
-  <si>
-    <t>If volcano has a source of permanent water/ice on edifice, water volume &gt;10^6 m3, there are rivers in close proximity or there is a known aquifer underground</t>
   </si>
   <si>
     <t>Most littoral hazards occur in coastal settings, however lava flow interaction with surface water can produce significant hazards (Boreham et al., 2020)</t>
@@ -637,6 +631,12 @@
   </si>
   <si>
     <t xml:space="preserve">Williams, G. T. (2016). The vulnerablity of Auckland city’s buildings to tephra hazards. [University of Canterbury]. https://doi.org/10.26021/5816 </t>
+  </si>
+  <si>
+    <t>If volcano has a source of permanent water/ice on edifice, water volume &gt;10^6 m3, there are rivers in close proximity or there is a known aquifer  (&gt;10km) underground</t>
+  </si>
+  <si>
+    <t>If volcano has a source of permanent water/ice on edifice, water volume &gt;10^6 m3, or there is a known aquifer (&lt;10km) underground</t>
   </si>
 </sst>
 </file>
@@ -1547,6 +1547,12 @@
     <xf numFmtId="0" fontId="19" fillId="15" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="11" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1572,12 +1578,6 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="33" xfId="5" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2100,47 +2100,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="92" t="s">
-        <v>81</v>
-      </c>
-      <c r="B1" s="93"/>
-      <c r="C1" s="94"/>
+      <c r="A1" s="94" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1" s="95"/>
+      <c r="C1" s="96"/>
     </row>
     <row r="2" spans="1:3" ht="75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="79" t="s">
-        <v>82</v>
-      </c>
-      <c r="B2" s="95" t="s">
-        <v>102</v>
-      </c>
-      <c r="C2" s="96"/>
+        <v>80</v>
+      </c>
+      <c r="B2" s="97" t="s">
+        <v>100</v>
+      </c>
+      <c r="C2" s="98"/>
     </row>
     <row r="3" spans="1:3" ht="158.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="79" t="s">
-        <v>83</v>
-      </c>
-      <c r="B3" s="97" t="s">
-        <v>104</v>
-      </c>
-      <c r="C3" s="98"/>
+        <v>81</v>
+      </c>
+      <c r="B3" s="99" t="s">
+        <v>102</v>
+      </c>
+      <c r="C3" s="100"/>
     </row>
     <row r="4" spans="1:3" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="79" t="s">
-        <v>84</v>
-      </c>
-      <c r="B4" s="97" t="s">
-        <v>105</v>
-      </c>
-      <c r="C4" s="98"/>
+        <v>82</v>
+      </c>
+      <c r="B4" s="99" t="s">
+        <v>103</v>
+      </c>
+      <c r="C4" s="100"/>
     </row>
     <row r="5" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A5" s="80" t="s">
-        <v>85</v>
-      </c>
-      <c r="B5" s="99">
+        <v>83</v>
+      </c>
+      <c r="B5" s="101">
         <v>45943</v>
       </c>
-      <c r="C5" s="100"/>
+      <c r="C5" s="102"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="70"/>
@@ -2148,60 +2148,60 @@
       <c r="C6" s="71"/>
     </row>
     <row r="7" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="101" t="s">
-        <v>86</v>
-      </c>
-      <c r="B7" s="102"/>
+      <c r="A7" s="92" t="s">
+        <v>84</v>
+      </c>
+      <c r="B7" s="93"/>
       <c r="C7" s="71"/>
     </row>
     <row r="8" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A8" s="81" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B8" s="82" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C8" s="71"/>
     </row>
     <row r="9" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A9" s="81" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B9" s="83" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C9" s="71"/>
     </row>
     <row r="10" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A10" s="81" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B10" s="83" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C10" s="71"/>
     </row>
     <row r="11" spans="1:3" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A11" s="84" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B11" s="83" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C11" s="71"/>
     </row>
     <row r="12" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="1:3" ht="23" x14ac:dyDescent="0.5">
       <c r="A13" s="72" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="73" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B15" s="73" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="28.5" thickTop="1" x14ac:dyDescent="0.3">
@@ -2209,7 +2209,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="75" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="28" x14ac:dyDescent="0.3">
@@ -2217,7 +2217,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="75" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.3">
@@ -2225,7 +2225,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="75" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="28" x14ac:dyDescent="0.3">
@@ -2233,7 +2233,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="78" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="30.4" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -2544,7 +2544,7 @@
         <v>20</v>
       </c>
       <c r="D3" s="24" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="25" x14ac:dyDescent="0.25">
@@ -2558,7 +2558,7 @@
         <v>16</v>
       </c>
       <c r="D4" s="24" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="25" x14ac:dyDescent="0.25">
@@ -2572,7 +2572,7 @@
         <v>12</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="25" x14ac:dyDescent="0.25">
@@ -2586,7 +2586,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="25" x14ac:dyDescent="0.25">
@@ -2600,7 +2600,7 @@
         <v>4</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="25" x14ac:dyDescent="0.25">
@@ -2614,7 +2614,7 @@
         <v>0</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="75" x14ac:dyDescent="0.25">
@@ -2628,7 +2628,7 @@
         <v>4</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2694,12 +2694,12 @@
         <v>7</v>
       </c>
       <c r="D3" s="31" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="62.5" x14ac:dyDescent="0.25">
       <c r="A4" s="32" t="s">
-        <v>29</v>
+        <v>135</v>
       </c>
       <c r="B4" s="59" t="b">
         <v>0</v>
@@ -2708,12 +2708,12 @@
         <v>5</v>
       </c>
       <c r="D4" s="33" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="34" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B5" s="59" t="b">
         <v>0</v>
@@ -2722,12 +2722,12 @@
         <v>3</v>
       </c>
       <c r="D5" s="33" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="52" x14ac:dyDescent="0.3">
       <c r="A6" s="35" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B6" s="59" t="b">
         <v>0</v>
@@ -2736,12 +2736,12 @@
         <v>2</v>
       </c>
       <c r="D6" s="33" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="25" x14ac:dyDescent="0.25">
       <c r="A7" s="32" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B7" s="59" t="b">
         <v>0</v>
@@ -2750,12 +2750,12 @@
         <v>2</v>
       </c>
       <c r="D7" s="109" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="25" x14ac:dyDescent="0.25">
       <c r="A8" s="32" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B8" s="59" t="b">
         <v>0</v>
@@ -2801,7 +2801,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="13" x14ac:dyDescent="0.3">
       <c r="A1" s="108" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B1" s="107"/>
       <c r="C1" s="107"/>
@@ -2825,7 +2825,7 @@
     </row>
     <row r="3" spans="1:5" ht="25" x14ac:dyDescent="0.25">
       <c r="A3" s="119" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B3" s="118"/>
       <c r="C3" s="60" t="b">
@@ -2835,12 +2835,12 @@
         <v>8</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="38" x14ac:dyDescent="0.3">
       <c r="A4" s="111" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B4" s="107"/>
       <c r="C4" s="59" t="b">
@@ -2850,12 +2850,12 @@
         <v>4</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="33.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="120" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B5" s="107"/>
       <c r="C5" s="59" t="b">
@@ -2865,12 +2865,12 @@
         <v>2</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="27.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="111" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B6" s="107"/>
       <c r="C6" s="59" t="b">
@@ -2880,15 +2880,15 @@
         <v>2</v>
       </c>
       <c r="E6" s="36" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="13" x14ac:dyDescent="0.3">
       <c r="A7" s="112" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="37" t="s">
         <v>43</v>
-      </c>
-      <c r="B7" s="37" t="s">
-        <v>44</v>
       </c>
       <c r="C7" s="59" t="b">
         <v>0</v>
@@ -2897,13 +2897,13 @@
         <v>2</v>
       </c>
       <c r="E7" s="115" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="13" x14ac:dyDescent="0.3">
       <c r="A8" s="113"/>
       <c r="B8" s="37" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C8" s="59" t="b">
         <v>0</v>
@@ -2916,7 +2916,7 @@
     <row r="9" spans="1:5" ht="13" x14ac:dyDescent="0.3">
       <c r="A9" s="114"/>
       <c r="B9" s="38" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" s="61" t="b">
         <v>0</v>
@@ -2994,7 +2994,7 @@
     <row r="3" spans="1:5" ht="26" x14ac:dyDescent="0.3">
       <c r="A3" s="37"/>
       <c r="B3" s="85" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C3" s="60" t="b">
         <v>0</v>
@@ -3003,12 +3003,12 @@
         <v>1</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="26" x14ac:dyDescent="0.3">
       <c r="B4" s="35" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C4" s="59" t="b">
         <v>0</v>
@@ -3017,12 +3017,12 @@
         <v>2</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="62.5" x14ac:dyDescent="0.25">
       <c r="B5" s="32" t="s">
-        <v>29</v>
+        <v>135</v>
       </c>
       <c r="C5" s="59" t="b">
         <v>0</v>
@@ -3031,12 +3031,12 @@
         <v>3</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="50" x14ac:dyDescent="0.25">
       <c r="B6" s="41" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C6" s="61" t="b">
         <v>0</v>
@@ -3045,7 +3045,7 @@
         <v>4</v>
       </c>
       <c r="E6" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3065,10 +3065,10 @@
     </row>
     <row r="9" spans="1:5" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A9" s="121" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" s="32" t="s">
         <v>55</v>
-      </c>
-      <c r="B9" s="32" t="s">
-        <v>56</v>
       </c>
       <c r="C9" s="59" t="b">
         <v>0</v>
@@ -3077,13 +3077,13 @@
         <v>2</v>
       </c>
       <c r="E9" s="33" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="50" x14ac:dyDescent="0.25">
       <c r="A10" s="107"/>
       <c r="B10" s="41" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C10" s="61" t="b">
         <v>0</v>
@@ -3092,7 +3092,7 @@
         <v>8</v>
       </c>
       <c r="E10" s="42" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3115,10 +3115,10 @@
     </row>
     <row r="13" spans="1:5" ht="25" x14ac:dyDescent="0.25">
       <c r="A13" s="121" t="s">
+        <v>57</v>
+      </c>
+      <c r="B13" s="32" t="s">
         <v>58</v>
-      </c>
-      <c r="B13" s="32" t="s">
-        <v>59</v>
       </c>
       <c r="C13" s="59" t="b">
         <v>0</v>
@@ -3127,13 +3127,13 @@
         <v>3</v>
       </c>
       <c r="E13" s="36" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="62.5" x14ac:dyDescent="0.25">
       <c r="A14" s="107"/>
       <c r="B14" s="32" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C14" s="59" t="b">
         <v>0</v>
@@ -3142,13 +3142,13 @@
         <v>6</v>
       </c>
       <c r="E14" s="36" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="39" x14ac:dyDescent="0.3">
       <c r="A15" s="107"/>
       <c r="B15" s="48" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C15" s="59" t="b">
         <v>0</v>
@@ -3157,13 +3157,13 @@
         <v>9</v>
       </c>
       <c r="E15" s="36" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="26" x14ac:dyDescent="0.3">
       <c r="A16" s="107"/>
       <c r="B16" s="48" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C16" s="59" t="b">
         <v>0</v>
@@ -3172,13 +3172,13 @@
         <v>12</v>
       </c>
       <c r="E16" s="33" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="26" x14ac:dyDescent="0.3">
       <c r="A17" s="107"/>
       <c r="B17" s="48" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C17" s="59" t="b">
         <v>0</v>
@@ -3187,13 +3187,13 @@
         <v>0</v>
       </c>
       <c r="E17" s="36" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="26" x14ac:dyDescent="0.3">
       <c r="A18" s="107"/>
       <c r="B18" s="49" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C18" s="61" t="b">
         <v>0</v>
@@ -3202,7 +3202,7 @@
         <v>1</v>
       </c>
       <c r="E18" s="36" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="13" x14ac:dyDescent="0.3">
@@ -3216,7 +3216,7 @@
     </row>
     <row r="21" spans="1:5" ht="13" x14ac:dyDescent="0.3">
       <c r="C21" s="26" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D21" s="27">
         <f>D20/2</f>
@@ -3270,7 +3270,7 @@
     </row>
     <row r="3" spans="1:4" ht="26" x14ac:dyDescent="0.3">
       <c r="A3" s="50" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B3" s="62" t="b">
         <v>0</v>
@@ -3279,12 +3279,12 @@
         <v>12</v>
       </c>
       <c r="D3" s="52" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="28" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="53" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B4" s="59" t="b">
         <v>0</v>
@@ -3293,12 +3293,12 @@
         <v>2</v>
       </c>
       <c r="D4" s="54" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="25.5" x14ac:dyDescent="0.3">
       <c r="A5" s="53" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B5" s="59" t="b">
         <v>0</v>
@@ -3307,12 +3307,12 @@
         <v>3</v>
       </c>
       <c r="D5" s="54" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="25.5" x14ac:dyDescent="0.3">
       <c r="A6" s="55" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B6" s="63" t="b">
         <v>0</v>
@@ -3321,7 +3321,7 @@
         <v>3</v>
       </c>
       <c r="D6" s="57" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="13" x14ac:dyDescent="0.3">
@@ -3356,7 +3356,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="13" x14ac:dyDescent="0.3">
       <c r="A1" s="108" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B1" s="107"/>
       <c r="C1" s="107"/>
@@ -3378,7 +3378,7 @@
     </row>
     <row r="3" spans="1:4" ht="26" x14ac:dyDescent="0.3">
       <c r="A3" s="53" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B3" s="59" t="b">
         <v>0</v>
@@ -3387,12 +3387,12 @@
         <v>2</v>
       </c>
       <c r="D3" s="87" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="32.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="58" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B4" s="59" t="b">
         <v>0</v>
@@ -3401,12 +3401,12 @@
         <v>1</v>
       </c>
       <c r="D4" s="24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="58" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B5" s="59" t="b">
         <v>0</v>
@@ -3415,12 +3415,12 @@
         <v>11</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="78" x14ac:dyDescent="0.3">
       <c r="A6" s="58" t="s">
-        <v>79</v>
+        <v>134</v>
       </c>
       <c r="B6" s="59" t="b">
         <v>0</v>
@@ -3429,7 +3429,7 @@
         <v>6</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="13" x14ac:dyDescent="0.3">
@@ -3461,7 +3461,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="28.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="88" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="28.9" customHeight="1" x14ac:dyDescent="0.45">
@@ -3469,115 +3469,115 @@
     </row>
     <row r="3" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A3" s="91" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B3" s="69"/>
     </row>
     <row r="4" spans="1:2" ht="28" x14ac:dyDescent="0.3">
       <c r="A4" s="89" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B4" s="69"/>
     </row>
     <row r="5" spans="1:2" ht="28" x14ac:dyDescent="0.3">
       <c r="A5" s="89" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B5" s="69"/>
     </row>
     <row r="6" spans="1:2" ht="28" x14ac:dyDescent="0.3">
       <c r="A6" s="89" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B6" s="69"/>
     </row>
     <row r="7" spans="1:2" ht="42" x14ac:dyDescent="0.3">
       <c r="A7" s="89" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B7" s="69"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="89" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B8" s="69"/>
     </row>
     <row r="9" spans="1:2" ht="28" x14ac:dyDescent="0.3">
       <c r="A9" s="89" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B9" s="69"/>
     </row>
     <row r="10" spans="1:2" ht="28" x14ac:dyDescent="0.3">
       <c r="A10" s="89" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B10" s="69"/>
     </row>
     <row r="11" spans="1:2" ht="42" x14ac:dyDescent="0.3">
       <c r="A11" s="89" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B11" s="69"/>
     </row>
     <row r="12" spans="1:2" ht="28" x14ac:dyDescent="0.3">
       <c r="A12" s="89" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B12" s="69"/>
     </row>
     <row r="13" spans="1:2" ht="28" x14ac:dyDescent="0.3">
       <c r="A13" s="89" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B13" s="69"/>
     </row>
     <row r="14" spans="1:2" ht="28" x14ac:dyDescent="0.3">
       <c r="A14" s="89" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B14" s="69"/>
     </row>
     <row r="15" spans="1:2" ht="28" x14ac:dyDescent="0.3">
       <c r="A15" s="89" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B15" s="69"/>
     </row>
     <row r="16" spans="1:2" ht="42" x14ac:dyDescent="0.3">
       <c r="A16" s="89" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B16" s="69"/>
     </row>
     <row r="17" spans="1:2" ht="28" x14ac:dyDescent="0.3">
       <c r="A17" s="89" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B17" s="69"/>
     </row>
     <row r="18" spans="1:2" ht="42" x14ac:dyDescent="0.3">
       <c r="A18" s="89" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B18" s="69"/>
     </row>
     <row r="19" spans="1:2" ht="28" x14ac:dyDescent="0.3">
       <c r="A19" s="89" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B19" s="69"/>
     </row>
     <row r="20" spans="1:2" ht="28" x14ac:dyDescent="0.3">
       <c r="A20" s="89" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B20" s="69"/>
     </row>
     <row r="21" spans="1:2" ht="28" x14ac:dyDescent="0.3">
       <c r="A21" s="89" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B21" s="69"/>
     </row>
